--- a/cases/Case_14bus_v2/ieee14AC_with_dc_mod.xlsx
+++ b/cases/Case_14bus_v2/ieee14AC_with_dc_mod.xlsx
@@ -1658,7 +1658,7 @@
         <v>138</v>
       </c>
       <c r="G9" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="H9" t="n">
         <v>0.118</v>
